--- a/Result/profitability/3545.xlsx
+++ b/Result/profitability/3545.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.53</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.3050000000000002</v>
+        <v>-0.3262500000000002</v>
       </c>
       <c r="N2" t="n">
-        <v>22.97875</v>
+        <v>22.9775</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.37</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3575000000000002</v>
+        <v>-0.3875000000000002</v>
       </c>
       <c r="N3" t="n">
-        <v>22.30625</v>
+        <v>22.415</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,16 +899,16 @@
         <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.3400000000000002</v>
+        <v>-0.3625000000000002</v>
       </c>
       <c r="N4" t="n">
-        <v>22.06125</v>
+        <v>21.4825</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
@@ -917,7 +917,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.18</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4175000000000001</v>
+        <v>-0.3850000000000002</v>
       </c>
       <c r="N5" t="n">
-        <v>21.175</v>
+        <v>20.8225</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.32</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4225000000000002</v>
+        <v>-0.3937500000000002</v>
       </c>
       <c r="N6" t="n">
-        <v>20.0625</v>
+        <v>19.575</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.64</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3912500000000002</v>
+        <v>0.4599999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>19.47125</v>
+        <v>19.65625</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1288,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" t="n">
         <v>98.2</v>
@@ -1391,10 +1391,10 @@
         <v>0.83</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4862499999999998</v>
+        <v>0.5612499999999998</v>
       </c>
       <c r="N8" t="n">
-        <v>19.3975</v>
+        <v>19.3025</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.47</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5424999999999999</v>
+        <v>0.5424999999999998</v>
       </c>
       <c r="N9" t="n">
         <v>18.69875</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3545</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2755</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2142</v>
+      </c>
+      <c r="E75" t="n">
+        <v>613</v>
+      </c>
+      <c r="F75" t="n">
+        <v>22.26</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-164</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-5.96%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>281</v>
+      </c>
+      <c r="J75" t="n">
+        <v>117</v>
+      </c>
+      <c r="K75" t="n">
+        <v>131</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.2937500000000002</v>
+      </c>
+      <c r="N75" t="n">
+        <v>23.48125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="X75" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.759999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.03301476976542128</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.7222222222222223</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-2.819999999999997</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1124401913875597</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
